--- a/output/pdf_financials_xlsx/ARL.xlsx
+++ b/output/pdf_financials_xlsx/ARL.xlsx
@@ -763,13 +763,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="17">
@@ -871,13 +871,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="21">
@@ -937,13 +937,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="24">
@@ -1005,13 +1005,13 @@
         <v>14.30629</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>14.832633</v>
+        <v>-14.832633</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>22.427122</v>
+        <v>-22.427122</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22.699651</v>
+        <v>-22.699651</v>
       </c>
     </row>
     <row r="27">
@@ -1027,13 +1027,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="28">
@@ -1071,13 +1071,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="30">
@@ -1125,13 +1125,13 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.148948</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -4621,7 +4621,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6686,10 +6690,10 @@
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0.976085</v>
+        <v>-0.976085</v>
       </c>
     </row>
     <row r="79">
@@ -6981,10 +6985,10 @@
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.444979</v>
+        <v>-0.444979</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>1.098929</v>
+        <v>-1.098929</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ARL.xlsx
+++ b/output/pdf_financials_xlsx/ARL.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019829</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.062581</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.010251</v>
       </c>
     </row>
     <row r="13">
@@ -1027,13 +1027,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.444979</v>
+        <v>-0.464808</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.098929</v>
+        <v>-1.16151</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.976085</v>
+        <v>-0.986336</v>
       </c>
     </row>
     <row r="28">
@@ -1071,13 +1071,13 @@
         <v>-0.443495</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.444979</v>
+        <v>-0.464808</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.098929</v>
+        <v>-1.16151</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.976085</v>
+        <v>-0.986336</v>
       </c>
     </row>
     <row r="30">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.579913</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.705653</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.579913</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.705653</v>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.613362</v>
+        <v>0.033449</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">

--- a/output/pdf_financials_xlsx/ARL.xlsx
+++ b/output/pdf_financials_xlsx/ARL.xlsx
@@ -565,13 +565,13 @@
         <v>0.000362</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.001618</v>
+        <v>0.001668</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.429212</v>
+        <v>0.475043</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.286696</v>
+        <v>0.310797</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
         <v>0.464808</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.429212</v>
+        <v>0.475043</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.286696</v>
+        <v>0.310797</v>
       </c>
     </row>
     <row r="11">
@@ -2715,13 +2715,13 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.043036</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.060034</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.052908</v>
       </c>
     </row>
     <row r="102">
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1e-06</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -4744,7 +4744,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5326,7 +5330,11 @@
           <t>HST receivables</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5539,7 +5547,11 @@
           <t>Proceeds from share issuance 7</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5834,7 +5846,11 @@
           <t>Repurchase of share 6</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5875,7 +5891,11 @@
           <t>Shares issued for cash 6</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.591519</v>
       </c>
@@ -6378,7 +6398,11 @@
           <t>Occupancy and office expenses</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
